--- a/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7767,6 +7767,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C441" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7778,7 +7789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13725,6 +13736,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-72.5</v>
+      </c>
+      <c r="C441" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13736,7 +13758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19683,6 +19705,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="C441" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19694,7 +19727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O438"/>
+  <dimension ref="A1:O439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25601,6 +25634,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B439" t="n">
+        <v>-95</v>
+      </c>
+      <c r="C439" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25612,7 +25656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31556,6 +31600,17 @@
         <v>-90</v>
       </c>
       <c r="C440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C441" t="n">
         <v>0</v>
       </c>
     </row>

--- a/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7778,6 +7778,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7789,7 +7800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13747,6 +13758,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-72.5</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13758,7 +13780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19716,6 +19738,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19727,7 +19760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O439"/>
+  <dimension ref="A1:O440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25645,6 +25678,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B440" t="n">
+        <v>-95</v>
+      </c>
+      <c r="C440" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25656,7 +25700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31611,6 +31655,17 @@
         <v>-90</v>
       </c>
       <c r="C441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C442" t="n">
         <v>0</v>
       </c>
     </row>

--- a/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7789,6 +7789,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7800,7 +7811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13769,6 +13780,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-75</v>
+      </c>
+      <c r="C443" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13780,7 +13802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19749,6 +19771,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19760,7 +19793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O440"/>
+  <dimension ref="A1:O441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25689,6 +25722,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B441" t="n">
+        <v>-95</v>
+      </c>
+      <c r="C441" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25700,7 +25744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31666,6 +31710,17 @@
         <v>-90</v>
       </c>
       <c r="C442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C443" t="n">
         <v>0</v>
       </c>
     </row>

--- a/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7800,6 +7800,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B444" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C444" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7811,7 +7822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13791,6 +13802,17 @@
         <v>-2.5</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B444" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="C444" t="n">
+        <v>-7.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13802,7 +13824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19782,6 +19804,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B444" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="C444" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19793,7 +19826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O441"/>
+  <dimension ref="A1:O442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25733,6 +25766,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B442" t="n">
+        <v>-95</v>
+      </c>
+      <c r="C442" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25744,7 +25788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31721,6 +31765,17 @@
         <v>-90</v>
       </c>
       <c r="C443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B444" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C444" t="n">
         <v>0</v>
       </c>
     </row>

--- a/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O444"/>
+  <dimension ref="A1:O445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7811,6 +7811,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B445" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C445" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7822,7 +7833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O444"/>
+  <dimension ref="A1:O445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13813,6 +13824,17 @@
         <v>-7.5</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B445" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C445" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13824,7 +13846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O444"/>
+  <dimension ref="A1:O445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19815,6 +19837,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B445" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="C445" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19826,7 +19859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O442"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25777,6 +25810,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B443" t="n">
+        <v>-95</v>
+      </c>
+      <c r="C443" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25788,7 +25832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O444"/>
+  <dimension ref="A1:O445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31776,6 +31820,17 @@
         <v>-90</v>
       </c>
       <c r="C444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B445" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C445" t="n">
         <v>0</v>
       </c>
     </row>

--- a/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7841,6 +7841,17 @@
         <v>-90</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="8" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B448" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7852,7 +7863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13873,6 +13884,17 @@
         <v>-85</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="8" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B448" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13884,7 +13906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19905,6 +19927,17 @@
         <v>-97.5</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="8" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B448" t="n">
+        <v>-97.5</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19916,7 +19949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O445"/>
+  <dimension ref="A1:O446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25897,6 +25930,17 @@
         <v>-105</v>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" s="8" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B446" t="n">
+        <v>-105</v>
+      </c>
+      <c r="C446" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25908,7 +25952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31927,6 +31971,17 @@
       </c>
       <c r="B447" t="n">
         <v>-100</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="8" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B448" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C448" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
+++ b/玉米大豆历史数据/大豆基差/North Dakota Basis.xlsx
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7852,6 +7852,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" s="8" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B449" t="n">
+        <v>-90</v>
+      </c>
+      <c r="C449" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7863,7 +7874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13895,6 +13906,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" s="8" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B449" t="n">
+        <v>-85</v>
+      </c>
+      <c r="C449" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13906,7 +13928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19938,6 +19960,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" s="8" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B449" t="n">
+        <v>-97.5</v>
+      </c>
+      <c r="C449" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19949,7 +19982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O446"/>
+  <dimension ref="A1:O447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25941,6 +25974,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" s="8" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B447" t="n">
+        <v>-105</v>
+      </c>
+      <c r="C447" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25952,7 +25996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31981,6 +32025,17 @@
         <v>-100</v>
       </c>
       <c r="C448" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="8" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B449" t="n">
+        <v>-100</v>
+      </c>
+      <c r="C449" t="n">
         <v>0</v>
       </c>
     </row>
